--- a/mistral_translate_work/split_by_prompt/excel/phantom_skill/lang_phantom/lang_phantom__phantom_skill__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/phantom_skill/lang_phantom/lang_phantom__phantom_skill__part_0001.xlsx
@@ -578,7 +578,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
         <is>
           <t>Biến hình thành Stonewall Brace và lao về phía trước, mỗi lần gây {0}% DMG. Giữ nút kỹ năng để kéo dài thời gian lao tối đa {1} giây.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         <is>
           <t>Summon Vanguard Junrock để lao về phía trước, gây {0}% Physical DMG cho kẻ địch trên đường đi.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <is>
           <t>Summon Fission Junrock để hồi máu 4 lần, phục hồi tổng cộng {0}% máu tối đa cho nhân vật cộng thêm {1} máu.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
         <is>
           <t>Summon Snip Snap để bắn các luồng nổ, gây tổng cộng 2 giai đoạn {0}% Fusion DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
         <is>
           <t>Summon Whiff Whaff để thực hiện các đòn hít vào, mỗi giai đoạn hít vào gây {0}% Aero DMG, trong khi vụ nổ gây {1}% Aero DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
         <is>
           <t>Summon Zig Zag để bắn chùm năng lượng, gây {0}% Spectro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
         <is>
           <t>Summon Tic Tac để lao tới, va chạm và hất tung kẻ địch lên không, lần lượt gây {0}% và {1}% Havoc DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11342,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         <is>
           <t>Summon một Glacio Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Glacio trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11618,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11963,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12653,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
         <is>
           <t>Summon một Thermo Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Thermo trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13274,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13412,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13619,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13688,7 +13688,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13757,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14171,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14240,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
         <is>
           <t>Summon một Spectro Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có Spectro trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14723,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14792,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14861,7 +14861,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15344,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15413,7 +15413,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         <is>
           <t>Summon một Rupture Prism tồn tại trong 7 giây. Nó sẽ liên tục phục hồi Resonance Energy cho các nhân vật có thuộc tính Rupture trong phạm vi hiệu quả với tốc độ {0} đơn vị mỗi 0.2 giây.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -15756,9 +15756,9 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -15825,9 +15825,9 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -15894,9 +15894,9 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -15963,9 +15963,9 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16032,9 +16032,9 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16101,9 +16101,9 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16170,9 +16170,9 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16239,9 +16239,9 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16308,9 +16308,9 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16377,9 +16377,9 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16446,9 +16446,9 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16515,9 +16515,9 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16584,9 +16584,9 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16653,9 +16653,9 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16722,9 +16722,9 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16791,9 +16791,9 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16860,9 +16860,9 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16929,9 +16929,9 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -16998,9 +16998,9 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -17067,9 +17067,9 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Cooldown của kỹ năng này.
+          <t>Biến hình thành Fusion Warrior và bắt đầu phòng thủ. Trong thời gian này, bị tấn công có thể kích hoạt phản đòn, gây {0}% Fusion DMG khi thành công và giảm {1}% Thời gian hồi của kỹ năng này.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17138,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17207,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17483,7 +17483,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17828,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17897,7 +17897,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -17966,7 +17966,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18242,7 +18242,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18311,7 +18311,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
         <is>
           <t>Summon Rupture Warrior để tung đòn đánh hướng lên, gây {0}% Havoc DMG và hất tung kẻ địch lên không.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18518,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18587,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18725,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18863,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -18932,7 +18932,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19001,7 +19001,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19070,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19139,7 +19139,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19208,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19622,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19691,7 +19691,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19760,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
         <is>
           <t>Summon Glacio Predator để phóng lao băng. Khi lao chạm mục tiêu gây {0} Glacio DMG. Mỗi giai đoạn tập trung gây {1}% DMG, còn vụ nổ gây {2} Glacio DMG.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19898,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20036,7 +20036,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20174,7 +20174,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20243,7 +20243,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20312,7 +20312,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20381,7 +20381,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20450,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20519,7 +20519,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20588,7 +20588,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20726,7 +20726,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20795,7 +20795,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20864,7 +20864,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -21209,7 +21209,7 @@
         <is>
           <t>Summon Impulse Predator để phóng các đợt mũi tên, mỗi đợt gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -21278,7 +21278,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21347,7 +21347,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21485,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21554,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21623,7 +21623,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21830,7 +21830,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21899,7 +21899,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21968,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22037,7 +22037,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22106,7 +22106,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22175,7 +22175,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22244,7 +22244,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22313,7 +22313,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22520,7 +22520,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22589,7 +22589,7 @@
         <is>
           <t>Summon Pneuma Predator để phóng phi tiêu, gây {0} Aero DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2}</t>
+Thời gian hồi: {2}</t>
         </is>
       </c>
     </row>
@@ -22658,7 +22658,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -22727,7 +22727,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23003,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23072,7 +23072,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23141,7 +23141,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23210,7 +23210,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23279,7 +23279,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23348,7 +23348,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23555,7 +23555,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23624,7 +23624,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23693,7 +23693,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23831,7 +23831,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -23969,7 +23969,7 @@
         <is>
           <t>Biến hình thành Violet-Feathered Heron và lao về phía trước theo đường zigzag, gây {0}% Electro DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24107,7 +24107,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24176,7 +24176,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24245,7 +24245,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24314,7 +24314,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24383,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24521,7 +24521,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24590,7 +24590,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24797,7 +24797,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -24935,7 +24935,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25004,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25142,7 +25142,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25211,7 +25211,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25280,7 +25280,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25349,7 +25349,7 @@
         <is>
           <t>Biến hình thành Cyan-Feathered Heron và lao về phía trước trong khi xoay tròn, mỗi lần gây {0}% Aero DMG. Tối đa 3 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -25418,7 +25418,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25487,7 +25487,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25556,7 +25556,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25625,7 +25625,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25694,7 +25694,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25763,7 +25763,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25832,7 +25832,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25901,7 +25901,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -25970,7 +25970,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26039,7 +26039,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26108,7 +26108,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26177,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26315,7 +26315,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26384,7 +26384,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26453,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26591,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26660,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
         <is>
           <t>Biến hình thành Flute Instrumentalist và phóng tia sét xuyên thấu, gây {0} Electro DMG. Sau đó, các tia sét sẽ giáng xuống, mỗi tia gây {1} Electro DMG.
 Concerto Vibrancy: {2}
-Cooldown: {3}</t>
+Thời gian hồi: {3}</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -26867,7 +26867,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -26936,7 +26936,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27005,7 +27005,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27074,7 +27074,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27143,7 +27143,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27212,7 +27212,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27350,7 +27350,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27557,7 +27557,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27626,7 +27626,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27695,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27833,7 +27833,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27902,7 +27902,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -27971,7 +27971,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -28040,7 +28040,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -28109,7 +28109,7 @@
         <is>
           <t>Biến hình thành Tambourine Instrumentalist và tạo ra 12 quả cầu năng lượng bao quanh nhân vật. Các quả cầu gây {0}% Havoc DMG khi va chạm với kẻ địch.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -28178,7 +28178,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28247,7 +28247,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28316,7 +28316,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28523,7 +28523,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28592,7 +28592,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28661,7 +28661,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28730,7 +28730,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28799,7 +28799,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28868,7 +28868,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29006,7 +29006,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29075,7 +29075,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29144,7 +29144,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29213,7 +29213,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29282,7 +29282,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29351,7 +29351,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29420,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29489,7 @@
         <is>
           <t>Biến hình thành Rocksteady Guardian và đập hai lần, lần lượt gây {0}% và {1}% Havoc DMG. Các va chạm do đập gây {2}% Havoc DMG cho mỗi đợt sóng.
 Concerto Vibrancy: {3}
-Cooldown: {4} giây</t>
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -29558,7 +29558,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29696,7 +29696,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29765,7 +29765,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29834,7 +29834,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29903,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -29972,7 +29972,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30179,7 +30179,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30386,7 +30386,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30455,7 +30455,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30524,7 +30524,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30593,7 +30593,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30662,7 +30662,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30731,7 +30731,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30800,7 +30800,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30869,7 +30869,7 @@
         <is>
           <t>Biến hình thành Chasm Guardian để nhảy về phía trước và đập mạnh, gây {0}% Havoc DMG khi va chạm trong lúc nhảy và {1}% Havoc DMG khi đập xuống.
 Concerto Vibrancy: {2}
-Cooldown: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -30938,7 +30938,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31007,7 +31007,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31076,7 +31076,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31145,7 +31145,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31214,7 +31214,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31283,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31352,7 +31352,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31421,7 +31421,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31490,7 +31490,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31628,7 +31628,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31766,7 +31766,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31835,7 +31835,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -31973,7 +31973,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32042,7 +32042,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32111,7 +32111,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32180,7 +32180,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
         <is>
           <t>Summon Cruisewing để hồi {0} máu tổng cộng 4 lần.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32318,7 +32318,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32387,7 +32387,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32456,7 +32456,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32525,7 +32525,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32594,7 +32594,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32663,7 +32663,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32732,7 +32732,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32801,7 +32801,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32870,7 +32870,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -32939,7 +32939,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33008,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33146,7 +33146,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33215,7 +33215,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33284,7 +33284,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33422,7 +33422,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33491,7 +33491,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33560,7 +33560,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
         <is>
           <t>Summon Sabyr Boar để húc, gây {0}% Physical DMG.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33698,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33767,7 +33767,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33836,7 +33836,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33905,7 +33905,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -33974,7 +33974,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34043,7 +34043,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34112,7 +34112,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34181,7 +34181,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34250,7 +34250,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34319,7 +34319,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34388,7 +34388,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34457,7 +34457,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34526,7 +34526,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34595,7 +34595,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34664,7 +34664,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34733,7 +34733,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34802,7 +34802,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34871,7 +34871,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -34940,7 +34940,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
         <is>
           <t>Summon Gulpuff và phun bong bóng 3 lần. Kẻ địch bị bong bóng giữ lại chịu {0}% Glacio DMG và bị thổi bay lên không. Khi bong bóng vỡ, kẻ địch rơi xuống và chịu sát thương.
 Concerto Vibrancy: {1}
-Cooldown: {2} giây</t>
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
